--- a/CollectaMundo.Tests/TestResources/AllCombinations.xlsx
+++ b/CollectaMundo.Tests/TestResources/AllCombinations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo.Tests\TestResources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\CollectaMundo.Tests\TestResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B213A5BB-B142-4C6C-8735-32190F975F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B501C9E5-3B1B-4684-AA30-2035A3CA6F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="4890" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Combinations" sheetId="1" r:id="rId1"/>
@@ -541,8 +541,9 @@
     <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">

--- a/CollectaMundo.Tests/TestResources/AllCombinations.xlsx
+++ b/CollectaMundo.Tests/TestResources/AllCombinations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\CollectaMundo.Tests\TestResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B501C9E5-3B1B-4684-AA30-2035A3CA6F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF6A8D-5C0D-4E33-8ACC-CD3F03EB1BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
